--- a/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est au jardin avec maman. Léa roule sur le petit vélo. Jules le regarde. Son ventre se serre. Il dit : je suis jaloux. Maman écoute. Jules va près de Léa. Il dit : je voudrais demander un tour. Léa dit : encore le chemin. Jules attend. Les mains restent sur le guidon vide. Puis Léa s'arrête. Jules a son tour. Il pédale tout doux. Maman dit : tu as demandé un tour. Tu as attendu.</t>
+          <t>Jules est au jardin avec maman. Léa roule sur le petit vélo. Jules le regarde. Son ventre se serre. Je suis jaloux. Maman écoute. Jules va près de Léa. Je voudrais demander un tour. Encore le chemin. Jules attend. Les mains restent sur le guidon vide. Puis Léa s'arrête. Jules a son tour. Il pédale tout doux. Tu as demandé un tour. Tu as attendu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est au jardin avec maman. Léa roule sur le petit vélo. Jules le regarde. Son ventre se serre.
+narrateur|Je suis jaloux. Maman écoute.
+narrateur|Jules va près de Léa.
+narrateur|Je voudrais demander un tour.
+copine|Encore le chemin.
+narrateur|Jules attend. Les mains restent sur le guidon vide. Puis Léa s'arrête. Jules a son tour. Il pédale tout doux.
+maman|Tu as demandé un tour. Tu as attendu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1494,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jules veut le vélo. Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1523,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a dit : je suis jaloux. Il a demandé un tour.</t>
+          <t>Jules Je suis jaloux. Il a demandé un tour.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1665,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules
+enfant-f|Je suis jaloux. Il a demandé un tour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le vélo. Jules essuie ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Tu as demandé un tour. Tu as attendu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Jules veut le vélo. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
 enfant-f|Je suis jaloux. Il a demandé un tour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Maman range le vélo. Jules essuie ses mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules est jaloux du vélo</t>
+          <t>Le vélo d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina a le petit vélo. Amir dit qu'il est jaloux. Il demande un tour. Il attend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est au jardin avec maman. Léa roule sur le petit vélo. Jules le regarde. Son ventre se serre. Je suis jaloux. Maman écoute. Jules va près de Léa. Je voudrais demander un tour. Encore le chemin. Jules attend. Les mains restent sur le guidon vide. Puis Léa s'arrête. Jules a son tour. Il pédale tout doux. Tu as demandé un tour. Tu as attendu.</t>
+          <t>Une flaque ronde est sur le chemin. Le ciel s'y voit, tout petit. La pluie vient de s'arrêter. Les feuilles gouttent encore. Un vélo jaune est près de la haie. Sa béquille est dans la boue molle. Ça sent la terre mouillée. La haie sent le vert, tout fort. Un ver rose traverse le chemin. J'essuie le banc, Amir. Victorina a déjà le petit vélo. La flaque est ronde, papa. Oui. Elle tient le ciel. Le chemin est encore humide. En ce moment, Victorina roule. Le petit vélo avance sur le chemin. Les roues font un bruit mouillé. Amir le regarde. Son ventre se serre. Ses mains restent sur le guidon vide. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Amir va près de Victorina. Je voudrais demander un tour. Encore le chemin. On attend la réponse. Amir attend. Le guidon vide est un peu froid. Il compte les tours de roue. Un. Deux. Trois. Victorina va jusqu'à la haie. Puis elle s'arrête. C'est ton tour. Merci, Victorina. Amir a son tour. Il pédale tout doux. Une goutte tombe d'une feuille. Tu as demandé un tour. Tu as attendu. Bravo, Amir. Tu as fait du bon travail. J'ai dit : je suis jaloux. Puis tu as demandé. La flaque tremble un peu. Le ciel y danse, tout petit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est au jardin avec maman. Léa roule sur le petit vélo. Jules le regarde. Son ventre se serre.
-narrateur|Je suis jaloux. Maman écoute.
-narrateur|Jules va près de Léa.
-narrateur|Je voudrais demander un tour.
-copine|Encore le chemin.
-narrateur|Jules attend. Les mains restent sur le guidon vide. Puis Léa s'arrête. Jules a son tour. Il pédale tout doux.
-maman|Tu as demandé un tour. Tu as attendu.</t>
+          <t>narrateur|Une flaque ronde est sur le chemin.
+narrateur|Le ciel s'y voit, tout petit.
+narrateur|La pluie vient de s'arrêter.
+narrateur|Les feuilles gouttent encore.
+narrateur|Un vélo jaune est près de la haie.
+narrateur|Sa béquille est dans la boue molle.
+narrateur|Ça sent la terre mouillée.
+narrateur|La haie sent le vert, tout fort.
+narrateur|Un ver rose traverse le chemin.
+maman|J'essuie le banc, Amir.
+papa|Victorina a déjà le petit vélo.
+enfant-m|La flaque est ronde, papa.
+papa|Oui. Elle tient le ciel.
+maman|Le chemin est encore humide.
+narrateur|En ce moment, Victorina roule.
+narrateur|Le petit vélo avance sur le chemin.
+narrateur|Les roues font un bruit mouillé.
+narrateur|Amir le regarde.
+narrateur|Son ventre se serre.
+narrateur|Ses mains restent sur le guidon vide.
+enfant-m|Je suis jaloux.
+maman|Je t'écoute.
+papa|Jaloux, c'est cette envie.
+narrateur|Amir va près de Victorina.
+enfant-m|Je voudrais demander un tour.
+enfant-f|Encore le chemin.
+maman|On attend la réponse.
+narrateur|Amir attend.
+narrateur|Le guidon vide est un peu froid.
+narrateur|Il compte les tours de roue.
+narrateur|Un. Deux. Trois.
+narrateur|Victorina va jusqu'à la haie.
+narrateur|Puis elle s'arrête.
+enfant-f|C'est ton tour.
+enfant-m|Merci, Victorina.
+narrateur|Amir a son tour.
+narrateur|Il pédale tout doux.
+narrateur|Une goutte tombe d'une feuille.
+maman|Tu as demandé un tour.
+maman|Tu as attendu.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|J'ai dit : je suis jaloux.
+papa|Puis tu as demandé.
+narrateur|La flaque tremble un peu.
+narrateur|Le ciel y danse, tout petit.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jules veut le vélo. Que fait-il ?</t>
+          <t>Amir veut le vélo. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1423,14 +1474,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,7 +1553,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jules veut le vélo. Que fait-il ?</t>
+          <t>narrateur|Amir veut le vélo.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules Je suis jaloux. Il a demandé un tour.</t>
+          <t>Amir a nommé : jaloux. Il a demandé un tour. Il a attendu. Je suis jaloux. J'ai demandé un tour. Oui. Tu as attendu le chemin. Bravo. C'est du bon travail. Après, je redemande ? On demande. On attend. Les mains attendent, aussi. C'est le bon geste. La béquille a un peu de boue. La boue est douce, un peu froide. Jaloux, on le dit. Puis on demande un tour. Les feuilles gouttent encore, une à une.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1591,14 +1643,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,8 +1726,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules
-enfant-f|Je suis jaloux. Il a demandé un tour.</t>
+          <t>narrateur|Amir a nommé : jaloux.
+narrateur|Il a demandé un tour.
+narrateur|Il a attendu.
+enfant-m|Je suis jaloux.
+enfant-m|J'ai demandé un tour.
+maman|Oui. Tu as attendu le chemin.
+papa|Bravo. C'est du bon travail.
+enfant-f|Après, je redemande ?
+papa|On demande. On attend.
+enfant-m|Les mains attendent, aussi.
+maman|C'est le bon geste.
+narrateur|La béquille a un peu de boue.
+narrateur|La boue est douce, un peu froide.
+papa|Jaloux, on le dit.
+enfant-m|Puis on demande un tour.
+narrateur|Les feuilles gouttent encore, une à une.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le vélo. Jules essuie ses mains.</t>
+          <t>Maman range le vélo. Amir essuie ses mains. On pose le vélo près de la haie ? Oui, papa. Merci d'avoir demandé, Amir. Les roues sont un peu mouillées. On les laisse sécher. J'ai eu mon tour. Tu as attendu Victorina. Amir regarde la flaque. Elle est plus petite, maintenant. Le ciel s'en va, dans l'eau. Il était tout petit. Comme un miroir, sur le chemin. Le banc essuyé est un peu froid.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1764,14 +1830,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1909,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le vélo. Jules essuie ses mains.</t>
+          <t>narrateur|Maman range le vélo.
+narrateur|Amir essuie ses mains.
+papa|On pose le vélo près de la haie ?
+enfant-m|Oui, papa.
+maman|Merci d'avoir demandé, Amir.
+enfant-f|Les roues sont un peu mouillées.
+papa|On les laisse sécher.
+enfant-m|J'ai eu mon tour.
+maman|Tu as attendu Victorina.
+narrateur|Amir regarde la flaque.
+narrateur|Elle est plus petite, maintenant.
+papa|Le ciel s'en va, dans l'eau.
+enfant-m|Il était tout petit.
+maman|Comme un miroir, sur le chemin.
+narrateur|Le banc essuyé est un peu froid.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le vélo jaune sèche près de la haie. La flaque est presque partie. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1932,14 +2012,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,7 +2091,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
+maman|Tu as attendu. Bravo.
+papa|Le vélo jaune sèche près de la haie.
+narrateur|La flaque est presque partie.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une flaque ronde est sur le chemin. Le ciel s'y voit, tout petit. La pluie vient de s'arrêter. Les feuilles gouttent encore. Un vélo jaune est près de la haie. Sa béquille est dans la boue molle. Ça sent la terre mouillée. La haie sent le vert, tout fort. Un ver rose traverse le chemin. J'essuie le banc, Amir. Victorina a déjà le petit vélo. La flaque est ronde, papa. Oui. Elle tient le ciel. Le chemin est encore humide. En ce moment, Victorina roule. Le petit vélo avance sur le chemin. Les roues font un bruit mouillé. Amir le regarde. Son ventre se serre. Ses mains restent sur le guidon vide. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Amir va près de Victorina. Je voudrais demander un tour. Encore le chemin. On attend la réponse. Amir attend. Le guidon vide est un peu froid. Il compte les tours de roue. Un. Deux. Trois. Victorina va jusqu'à la haie. Puis elle s'arrête. C'est ton tour. Merci, Victorina. Amir a son tour. Il pédale tout doux. Une goutte tombe d'une feuille. Tu as demandé un tour. Tu as attendu. Bravo, Amir. Tu as fait du bon travail. J'ai dit : je suis jaloux. Puis tu as demandé. La flaque tremble un peu. Le ciel y danse, tout petit.</t>
+          <t>Une flaque ronde est sur le chemin. Le ciel s'y voit, tout petit. La pluie vient de s'arrêter. Les feuilles gouttent encore. Un vélo jaune est près de la haie. Sa béquille est dans la boue molle. Ça sent la terre mouillée. La haie sent le vert, tout fort. Un ver rose traverse le chemin. J'essuie le banc, Amir. Victorina a déjà le petit vélo. La flaque est ronde, papa. Oui. Elle tient le ciel. Le chemin est encore humide. En ce moment, Victorina roule. Le petit vélo avance sur le chemin. Les roues font un bruit mouillé. Amir le regarde. Son ventre se serre. Ses mains restent sur le guidon vide. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Amir va près de Victorina. Je voudrais demander un tour. Encore le chemin. On attend la réponse. Amir attend. Le guidon vide est un peu froid. Il compte les tours de roue. Un. Deux. Trois. Victorina va jusqu'à la haie. Puis elle s'arrête. C'est ton tour. Merci, Victorina. Amir a son tour. Il pédale tout doux. Une goutte tombe d'une feuille. Tu as demandé un tour. Tu as attendu. Bravo, Amir. J'ai dit : je suis jaloux. Puis tu as demandé. La flaque tremble un peu. Le ciel y danse, tout petit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules est au jardin avec maman. Léa roule sur le petit vélo. Jules le regarde. Son ventre se serre. Il dit : je suis &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Maman écoute. Jules va près de Léa. Il dit : je voudrais demander un tour. Léa dit : encore le chemin. Jules attend. Les mains restent sur le guidon vide. Puis Léa s'arrête. Jules a son tour. Il pédale tout doux. Maman dit : tu as demandé un tour. Tu as attendu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une flaque ronde est sur le chemin. Le ciel s'y voit, tout petit. La pluie vient de s'arrêter. Les feuilles gouttent encore. Un vélo jaune est près de la haie. Sa béquille est dans la boue molle. Ça sent la terre mouillée. La haie sent le vert, tout fort. Un ver rose traverse le chemin. J'essuie le banc, Amir. Victorina a déjà le petit vélo. La flaque est ronde, papa. Oui. Elle tient le ciel. Le chemin est encore humide. En ce moment, Victorina roule. Le petit vélo avance sur le chemin. Les roues font un bruit mouillé. Amir le regarde. Son ventre se serre. Ses mains restent sur le guidon vide. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Amir va près de Victorina. Je voudrais demander un tour. Encore le chemin. On attend la réponse. Amir attend. Le guidon vide est un peu froid. Il compte les tours de roue. Un. Deux. Trois. Victorina va jusqu'à la haie. Puis elle s'arrête. C'est ton tour. Merci, Victorina. Amir a son tour. Il pédale tout doux. Une goutte tombe d'une feuille. Tu as demandé un tour. Tu as attendu. Bravo, Amir. J'ai dit : je suis jaloux. Puis tu as demandé. La flaque tremble un peu. Le ciel y danse, tout petit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,14 +1365,12 @@
 maman|Tu as demandé un tour.
 maman|Tu as attendu.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
 enfant-m|J'ai dit : je suis jaloux.
 papa|Puis tu as demandé.
 narrateur|La flaque tremble un peu.
 narrateur|Le ciel y danse, tout petit.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1402,7 +1400,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules veut le vélo. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir veut le vélo. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1557,7 +1555,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1582,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a nommé : jaloux. Il a demandé un tour. Il a attendu. Je suis jaloux. J'ai demandé un tour. Oui. Tu as attendu le chemin. Bravo. C'est du bon travail. Après, je redemande ? On demande. On attend. Les mains attendent, aussi. C'est le bon geste. La béquille a un peu de boue. La boue est douce, un peu froide. Jaloux, on le dit. Puis on demande un tour. Les feuilles gouttent encore, une à une.</t>
+          <t>Amir a nommé : jaloux. Il a demandé un tour. Il a attendu. Je suis jaloux. J'ai demandé un tour. Oui. Tu as attendu le chemin. Après, je redemande ? On demande. On attend. Les mains attendent, aussi. C'est le bon geste. La béquille a un peu de boue. La boue est douce, un peu froide. Jaloux, on le dit. Puis on demande un tour. Les feuilles gouttent encore, une à une.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a dit : je suis &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Il a demandé un tour.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé : jaloux. Il a demandé un tour. Il a attendu. Je suis jaloux. J'ai demandé un tour. Oui. Tu as attendu le chemin. Après, je redemande ? On demande. On attend. Les mains attendent, aussi. C'est le bon geste. La béquille a un peu de boue. La boue est douce, un peu froide. Jaloux, on le dit. Puis on demande un tour. Les feuilles gouttent encore, une à une.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1732,7 +1729,6 @@
 enfant-m|Je suis jaloux.
 enfant-m|J'ai demandé un tour.
 maman|Oui. Tu as attendu le chemin.
-papa|Bravo. C'est du bon travail.
 enfant-f|Après, je redemande ?
 papa|On demande. On attend.
 enfant-m|Les mains attendent, aussi.
@@ -1744,7 +1740,6 @@
 narrateur|Les feuilles gouttent encore, une à une.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1774,7 +1769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le vélo. Jules essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range le vélo. Amir essuie ses mains. On pose le vélo près de la haie ? Oui, papa. Merci d'avoir demandé, Amir. Les roues sont un peu mouillées. On les laisse sécher. J'ai eu mon tour. Tu as attendu Victorina. Amir regarde la flaque. Elle est plus petite, maintenant. Le ciel s'en va, dans l'eau. Il était tout petit. Comme un miroir, sur le chemin. Le banc essuyé est un peu froid.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,7 +1921,6 @@
 narrateur|Le banc essuyé est un peu froid.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1951,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le vélo jaune sèche près de la haie. La flaque est presque partie. L'histoire est finie.</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le vélo jaune sèche près de la haie. La flaque est presque partie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le vélo jaune sèche près de la haie. La flaque est presque partie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,11 +2088,9 @@
           <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
 maman|Tu as attendu. Bravo.
 papa|Le vélo jaune sèche près de la haie.
-narrateur|La flaque est presque partie.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La flaque est presque partie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2117,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, Léa, maman</t>
+          <t>Amir, Victorina, papa, maman</t>
         </is>
       </c>
     </row>
